--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-02).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-02).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-181</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>R$ 757.854,37</t>
-  </si>
-  <si>
-    <t>R$ 3.967,82
-R$ 4.044,56</t>
-  </si>
-  <si>
-    <t>(2.7%)
-(0.8%)</t>
-  </si>
-  <si>
-    <t>45.1</t>
-  </si>
-  <si>
-    <t>(6.9%)</t>
-  </si>
-  <si>
-    <t>10.2%</t>
-  </si>
-  <si>
-    <t>(29.1%)</t>
+184</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>R$ 764.427,46</t>
+  </si>
+  <si>
+    <t>R$ 3.940,35
+R$ 4.014,34</t>
+  </si>
+  <si>
+    <t>(2.9%)
+(1.1%)</t>
+  </si>
+  <si>
+    <t>44.8</t>
+  </si>
+  <si>
+    <t>(7.1%)</t>
+  </si>
+  <si>
+    <t>8.6%</t>
+  </si>
+  <si>
+    <t>(30.7%)</t>
   </si>
   <si>
     <t>4.1%</t>
@@ -950,16 +950,16 @@
     <t>26.5</t>
   </si>
   <si>
-    <t>73.0%</t>
-  </si>
-  <si>
-    <t>8.4%</t>
+    <t>73.2%</t>
+  </si>
+  <si>
+    <t>8.3%</t>
   </si>
   <si>
     <t>4.7</t>
   </si>
   <si>
-    <t>7.1</t>
+    <t>7.0</t>
   </si>
   <si>
     <t>11.9</t>
@@ -968,13 +968,13 @@
     <t>18.5</t>
   </si>
   <si>
-    <t>72.8%</t>
-  </si>
-  <si>
-    <t>-R$ 23.584,52</t>
-  </si>
-  <si>
-    <t>2.97</t>
+    <t>72.9%</t>
+  </si>
+  <si>
+    <t>-R$ 23.618,68</t>
+  </si>
+  <si>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -5960,7 +5960,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5996,25 +5996,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>3390.8400000000001</v>
+      </c>
+      <c r="P36" s="5">
+        <v>3390.8400000000001</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.050068748529029206</v>
+      </c>
+      <c r="R36" s="7">
+        <v>43</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.048780487804878092</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.35635529839213881</v>
+      </c>
+      <c r="U36" s="6">
+        <v>0.015823158863290509</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.1334315390876597</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.073425758809026673</v>
+      </c>
+      <c r="X36" s="8">
+        <v>24.449999999999999</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>4.5359840909090909</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>4.0265756756756756</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>8.7756749999999997</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>15.727478378378379</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.83783783783783783</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>-34.159999999999997</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -7881,7 +7917,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7917,25 +7953,61 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
-      <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="O51" s="5">
+        <v>180.59999999999999</v>
+      </c>
+      <c r="P51" s="5">
+        <v>180.59999999999999</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.835830121445713</v>
+      </c>
+      <c r="R51" s="7">
+        <v>2</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.83333333333333337</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.33654485049833888</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.21988372093023256</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.48892026578073094</v>
+      </c>
+      <c r="X51" s="8">
+        <v>23.600000000000001</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>4.0333500000000004</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>7.4500000000000002</v>
+      </c>
+      <c r="AC51" s="8">
+        <v>11.050000000000001</v>
+      </c>
+      <c r="AD51" s="8">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>1</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -12640,7 +12712,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -12679,7 +12751,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12713,25 +12785,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>3001.6500000000001</v>
+      </c>
+      <c r="P89" s="5">
+        <v>3001.6500000000001</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.35946352549534255</v>
+      </c>
+      <c r="R89" s="7">
+        <v>33</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.2978723404255319</v>
+      </c>
+      <c r="T89" s="6">
+        <v>-4.2956619525927406</v>
+      </c>
+      <c r="U89" s="6">
+        <v>-4.6259402995019405</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.043492579081505167</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.010250862025885763</v>
+      </c>
+      <c r="X89" s="8">
+        <v>28.369049999999998</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>5.1568617647058828</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>8.6628230769230772</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>19.960714285714285</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.6428571428571429</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -15491,7 +15597,7 @@
         <v>0</v>
       </c>
       <c r="AH111" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI111" s="11"/>
       <c r="AJ111" s="13">
@@ -15844,7 +15950,7 @@
         <v>0</v>
       </c>
       <c r="AH114" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI114" s="11"/>
       <c r="AJ114" s="13">
@@ -16755,7 +16861,7 @@
         <v>0</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -17017,7 +17123,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -17410,7 +17516,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18587,7 +18693,7 @@
         <v>0</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -18718,7 +18824,7 @@
         <v>0</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -20905,7 +21011,7 @@
         <v>-416.02999999999997</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">
@@ -21032,7 +21138,7 @@
         <v>-0.02</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
@@ -22187,7 +22293,7 @@
         <v>0</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -24241,7 +24347,9 @@
       <c r="AB179" s="8">
         <v>0.84420434782608689</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>3.003622</v>
+      </c>
       <c r="AD179" s="8">
         <v>9.959421739130434</v>
       </c>
@@ -28326,7 +28434,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>
